--- a/data/trans_orig/P16A_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A_R-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11754</t>
+          <t>12176</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30438</t>
+          <t>29546</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14728</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33208</t>
+          <t>32240</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30228</t>
+          <t>30984</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55660</t>
+          <t>55039</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>443338</t>
+          <t>444230</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>462022</t>
+          <t>461600</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273472</t>
+          <t>274440</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>291952</t>
+          <t>292904</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>724797</t>
+          <t>725418</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>750229</t>
+          <t>749473</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9158</t>
+          <t>9289</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25936</t>
+          <t>28298</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23261</t>
+          <t>23380</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45256</t>
+          <t>45809</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36463</t>
+          <t>36327</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63996</t>
+          <t>63866</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>340998</t>
+          <t>338636</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>357776</t>
+          <t>357645</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>326609</t>
+          <t>326056</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>348604</t>
+          <t>348485</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>674803</t>
+          <t>674933</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>702336</t>
+          <t>702472</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,08%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20109</t>
+          <t>19247</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39140</t>
+          <t>39648</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14021</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30940</t>
+          <t>31471</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36926</t>
+          <t>36715</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64855</t>
+          <t>64697</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>503249</t>
+          <t>502741</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>522280</t>
+          <t>523142</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136842</t>
+          <t>136311</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153761</t>
+          <t>153361</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>645316</t>
+          <t>645474</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>673245</t>
+          <t>673456</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47305</t>
+          <t>47698</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78400</t>
+          <t>77799</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55559</t>
+          <t>56537</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>86832</t>
+          <t>89185</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110671</t>
+          <t>110075</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>154988</t>
+          <t>155600</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1159934</t>
+          <t>1160535</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1191029</t>
+          <t>1190636</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>627453</t>
+          <t>625100</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>658726</t>
+          <t>657748</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1797632</t>
+          <t>1797020</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1841949</t>
+          <t>1842545</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17095</t>
+          <t>17703</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36783</t>
+          <t>36197</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57968</t>
+          <t>60858</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>90917</t>
+          <t>92467</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81146</t>
+          <t>83997</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>119202</t>
+          <t>120920</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>313772</t>
+          <t>314358</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>333460</t>
+          <t>332852</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>477835</t>
+          <t>476285</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>510784</t>
+          <t>507894</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>800105</t>
+          <t>798387</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>838161</t>
+          <t>835310</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,86%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18543</t>
+          <t>19738</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>132172</t>
+          <t>128205</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>177792</t>
+          <t>176543</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>141548</t>
+          <t>139019</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>190793</t>
+          <t>187144</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279658</t>
+          <t>278463</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>293198</t>
+          <t>292798</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1070968</t>
+          <t>1072217</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1116588</t>
+          <t>1120555</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1356167</t>
+          <t>1359816</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1405412</t>
+          <t>1407941</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,01%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>137701</t>
+          <t>137683</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>185541</t>
+          <t>186340</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>338095</t>
+          <t>340547</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>407754</t>
+          <t>413888</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>492266</t>
+          <t>491676</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>583408</t>
+          <t>582337</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3084649</t>
+          <t>3083850</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3132489</t>
+          <t>3132507</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2970370</t>
+          <t>2964236</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3040029</t>
+          <t>3037577</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6064906</t>
+          <t>6065977</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6156048</t>
+          <t>6156638</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12893</t>
+          <t>12885</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33437</t>
+          <t>33876</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14446</t>
+          <t>15192</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34812</t>
+          <t>35654</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31757</t>
+          <t>31506</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61970</t>
+          <t>60223</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>403774</t>
+          <t>403335</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>424318</t>
+          <t>424326</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>279642</t>
+          <t>278800</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>300008</t>
+          <t>299262</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>689695</t>
+          <t>691442</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>719908</t>
+          <t>720159</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,81%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14507</t>
+          <t>14345</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36240</t>
+          <t>35968</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20017</t>
+          <t>20223</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43338</t>
+          <t>41960</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39078</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71229</t>
+          <t>69950</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>382557</t>
+          <t>382829</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>404290</t>
+          <t>404452</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>294673</t>
+          <t>296051</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>317994</t>
+          <t>317788</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>685579</t>
+          <t>686858</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>717730</t>
+          <t>718279</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49028</t>
+          <t>48265</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82615</t>
+          <t>81832</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35832</t>
+          <t>35988</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60178</t>
+          <t>60061</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89341</t>
+          <t>88946</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133822</t>
+          <t>131821</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>546800</t>
+          <t>547583</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>580387</t>
+          <t>581150</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>199951</t>
+          <t>200068</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>224297</t>
+          <t>224141</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>755722</t>
+          <t>757723</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>800203</t>
+          <t>800598</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,0%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64838</t>
+          <t>64114</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101855</t>
+          <t>100903</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85599</t>
+          <t>84376</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>124856</t>
+          <t>125062</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>158036</t>
+          <t>160350</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>214121</t>
+          <t>212897</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1057154</t>
+          <t>1058106</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1094171</t>
+          <t>1094895</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>641801</t>
+          <t>641595</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>681058</t>
+          <t>682281</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1711546</t>
+          <t>1712770</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1767631</t>
+          <t>1765317</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,67%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21221</t>
+          <t>20319</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41624</t>
+          <t>41334</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>129332</t>
+          <t>129808</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>173681</t>
+          <t>175243</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>157306</t>
+          <t>158197</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>210629</t>
+          <t>212203</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,68%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>468972</t>
+          <t>469262</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>489375</t>
+          <t>490277</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>587841</t>
+          <t>586279</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>632190</t>
+          <t>631714</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1061489</t>
+          <t>1059915</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1114812</t>
+          <t>1113921</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,56%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13712</t>
+          <t>15034</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>171979</t>
+          <t>171968</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>225058</t>
+          <t>222865</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>177402</t>
+          <t>177405</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>230203</t>
+          <t>231467</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>253170</t>
+          <t>251848</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264065</t>
+          <t>264095</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>884293</t>
+          <t>886486</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>937372</t>
+          <t>937383</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1146030</t>
+          <t>1144766</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1198831</t>
+          <t>1198828</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>195028</t>
+          <t>196629</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>256795</t>
+          <t>259899</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>509602</t>
+          <t>507890</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>598060</t>
+          <t>598701</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>726561</t>
+          <t>724127</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>839026</t>
+          <t>835017</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3165115</t>
+          <t>3162011</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3226882</t>
+          <t>3225281</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2952065</t>
+          <t>2951424</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3040523</t>
+          <t>3042235</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6133009</t>
+          <t>6137018</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6245474</t>
+          <t>6247908</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,61%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17558</t>
+          <t>17698</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39240</t>
+          <t>38812</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19788</t>
+          <t>19019</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41120</t>
+          <t>40048</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40698</t>
+          <t>40389</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70147</t>
+          <t>70233</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>389852</t>
+          <t>390280</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>411534</t>
+          <t>411394</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>305935</t>
+          <t>307007</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>327267</t>
+          <t>328036</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>706000</t>
+          <t>705914</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>735449</t>
+          <t>735758</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,8%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13661</t>
+          <t>12966</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32261</t>
+          <t>30490</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15361</t>
+          <t>14511</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35104</t>
+          <t>34502</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32016</t>
+          <t>32336</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58451</t>
+          <t>58693</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>344966</t>
+          <t>346737</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>363566</t>
+          <t>364261</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>337169</t>
+          <t>337771</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>356912</t>
+          <t>357762</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>691049</t>
+          <t>690807</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>717484</t>
+          <t>717164</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22174</t>
+          <t>20240</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44065</t>
+          <t>42312</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19790</t>
+          <t>19744</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41480</t>
+          <t>40518</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46868</t>
+          <t>46980</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77071</t>
+          <t>77996</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>477849</t>
+          <t>479602</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>499740</t>
+          <t>501674</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>124643</t>
+          <t>125605</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>146333</t>
+          <t>146379</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>610965</t>
+          <t>610040</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>641168</t>
+          <t>641056</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62622</t>
+          <t>65324</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100847</t>
+          <t>98848</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90389</t>
+          <t>88978</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131198</t>
+          <t>129358</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>162714</t>
+          <t>163630</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>216236</t>
+          <t>216723</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1048791</t>
+          <t>1050790</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1087016</t>
+          <t>1084314</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>694678</t>
+          <t>696518</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>735487</t>
+          <t>736898</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1759278</t>
+          <t>1758791</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1812800</t>
+          <t>1811884</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,72%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36369</t>
+          <t>35735</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62332</t>
+          <t>63000</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>141477</t>
+          <t>138236</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>188570</t>
+          <t>184435</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>182987</t>
+          <t>185074</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>238666</t>
+          <t>236675</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>558374</t>
+          <t>557706</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>584337</t>
+          <t>584971</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>549674</t>
+          <t>553809</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>596767</t>
+          <t>600008</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1120284</t>
+          <t>1122275</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1175963</t>
+          <t>1173876</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,38%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11052</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>162504</t>
+          <t>163137</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>215253</t>
+          <t>213892</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>166167</t>
+          <t>165319</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>222481</t>
+          <t>220102</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>276093</t>
+          <t>276036</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>285194</t>
+          <t>285234</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>866772</t>
+          <t>868133</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>919521</t>
+          <t>918888</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1146689</t>
+          <t>1149068</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1203003</t>
+          <t>1203851</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,93%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>185588</t>
+          <t>182057</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>241763</t>
+          <t>237958</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>490981</t>
+          <t>494142</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>580088</t>
+          <t>582954</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>690652</t>
+          <t>700256</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>804589</t>
+          <t>810815</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3143959</t>
+          <t>3147764</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3200134</t>
+          <t>3203665</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2951508</t>
+          <t>2948642</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3040615</t>
+          <t>3037454</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6112729</t>
+          <t>6106503</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6226666</t>
+          <t>6217062</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,88%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido algún psicofármaco en las dos últimas semanas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32043</t>
+          <t>32055</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56247</t>
+          <t>56868</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32975</t>
+          <t>33426</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53035</t>
+          <t>53233</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71393</t>
+          <t>69755</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103052</t>
+          <t>102987</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>448965</t>
+          <t>448344</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>473169</t>
+          <t>473157</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>394432</t>
+          <t>394234</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>414492</t>
+          <t>414041</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>849627</t>
+          <t>849692</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>881286</t>
+          <t>882924</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,68%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21539</t>
+          <t>21596</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41001</t>
+          <t>41966</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39848</t>
+          <t>41025</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60290</t>
+          <t>60947</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65033</t>
+          <t>66449</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94078</t>
+          <t>96723</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>411212</t>
+          <t>410247</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>430674</t>
+          <t>430617</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>322290</t>
+          <t>321633</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>342732</t>
+          <t>341555</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>740715</t>
+          <t>738070</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>769760</t>
+          <t>768344</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,04%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16778</t>
+          <t>16878</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77496</t>
+          <t>77198</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28315</t>
+          <t>27361</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44233</t>
+          <t>44306</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32046</t>
+          <t>35642</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>120968</t>
+          <t>119337</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>590768</t>
+          <t>591066</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>651486</t>
+          <t>651386</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>122678</t>
+          <t>122605</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>138596</t>
+          <t>139550</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>714207</t>
+          <t>715838</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>803129</t>
+          <t>799533</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80869</t>
+          <t>81570</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>114398</t>
+          <t>114953</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58663</t>
+          <t>68036</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>162610</t>
+          <t>161618</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>157643</t>
+          <t>147637</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>254007</t>
+          <t>254028</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,7 +9752,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>920421</t>
+          <t>919866</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>953950</t>
+          <t>953249</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>815484</t>
+          <t>816476</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>919431</t>
+          <t>910058</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1758905</t>
+          <t>1758884</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1855269</t>
+          <t>1865275</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41000</t>
+          <t>39263</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66959</t>
+          <t>65684</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>140705</t>
+          <t>144214</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>220514</t>
+          <t>224992</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>197680</t>
+          <t>199966</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>276830</t>
+          <t>273503</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>408087</t>
+          <t>409362</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>434046</t>
+          <t>435783</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>620821</t>
+          <t>616343</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>700630</t>
+          <t>697121</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1039551</t>
+          <t>1042878</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1118701</t>
+          <t>1116415</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,81%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29805</t>
+          <t>27764</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>135157</t>
+          <t>134898</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>171686</t>
+          <t>172910</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>145031</t>
+          <t>146400</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>186768</t>
+          <t>188761</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>210702</t>
+          <t>212743</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>234359</t>
+          <t>234144</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>589685</t>
+          <t>588461</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>626214</t>
+          <t>626473</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>815110</t>
+          <t>813117</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>856847</t>
+          <t>855478</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,39%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>215214</t>
+          <t>222762</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>318400</t>
+          <t>319678</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>484111</t>
+          <t>488075</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>649029</t>
+          <t>649604</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,47 +10746,47 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
+          <t>13,64%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>18,16%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1416</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>872578</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>756140</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>940658</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>12,55%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>10,87%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>13,53%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>18,14%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1416</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>872578</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>757378</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>953407</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>12,55%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>10,89%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3057660</t>
+          <t>3056382</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3160846</t>
+          <t>3153298</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2928729</t>
+          <t>2928154</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3093647</t>
+          <t>3089683</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,47 +10859,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>86,36%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>7128</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>6081240</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>6013160</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>6197678</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>87,45%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>86,47%</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>7128</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>6081240</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>6000411</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>6196440</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>87,45%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>86,29%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,13%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P16A_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12176</t>
+          <t>12038</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29546</t>
+          <t>29209</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13776</t>
+          <t>14028</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32240</t>
+          <t>31841</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30984</t>
+          <t>30554</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55039</t>
+          <t>55279</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>444230</t>
+          <t>444567</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>461600</t>
+          <t>461738</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274440</t>
+          <t>274839</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>292904</t>
+          <t>292652</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>725418</t>
+          <t>725178</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>749473</t>
+          <t>749903</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9289</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28298</t>
+          <t>26153</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23380</t>
+          <t>24022</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45809</t>
+          <t>45790</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36327</t>
+          <t>37576</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63866</t>
+          <t>64442</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>338636</t>
+          <t>340781</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>357645</t>
+          <t>357831</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>326056</t>
+          <t>326075</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>348485</t>
+          <t>347843</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>674933</t>
+          <t>674357</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>702472</t>
+          <t>701223</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19247</t>
+          <t>19697</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39648</t>
+          <t>40528</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>13800</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31471</t>
+          <t>31744</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36715</t>
+          <t>37835</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64697</t>
+          <t>63900</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>502741</t>
+          <t>501861</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>523142</t>
+          <t>522692</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136311</t>
+          <t>136038</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153361</t>
+          <t>153982</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>645474</t>
+          <t>646271</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>673456</t>
+          <t>672336</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47698</t>
+          <t>46182</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77799</t>
+          <t>77273</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56537</t>
+          <t>55895</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89185</t>
+          <t>87582</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110075</t>
+          <t>107960</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155600</t>
+          <t>153212</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1160535</t>
+          <t>1161061</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1190636</t>
+          <t>1192152</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>625100</t>
+          <t>626703</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>657748</t>
+          <t>658390</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1797020</t>
+          <t>1799408</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1842545</t>
+          <t>1844660</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,47%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17703</t>
+          <t>17163</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36197</t>
+          <t>37077</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60858</t>
+          <t>60101</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92467</t>
+          <t>94333</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83997</t>
+          <t>82044</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120920</t>
+          <t>119851</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>314358</t>
+          <t>313478</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>332852</t>
+          <t>333392</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>476285</t>
+          <t>474419</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>507894</t>
+          <t>508651</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>798387</t>
+          <t>799456</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>835310</t>
+          <t>837263</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,08%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19738</t>
+          <t>19106</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>128205</t>
+          <t>132046</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>176543</t>
+          <t>179411</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>139019</t>
+          <t>142051</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>187144</t>
+          <t>188389</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>278463</t>
+          <t>279095</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>292798</t>
+          <t>292826</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1072217</t>
+          <t>1069349</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1120555</t>
+          <t>1116714</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1359816</t>
+          <t>1358571</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1407941</t>
+          <t>1404909</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,82%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>137683</t>
+          <t>136820</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>186340</t>
+          <t>185420</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>340547</t>
+          <t>339864</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>413888</t>
+          <t>411282</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>491676</t>
+          <t>492741</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>582337</t>
+          <t>581184</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3083850</t>
+          <t>3084770</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3132507</t>
+          <t>3133370</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2964236</t>
+          <t>2966842</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3037577</t>
+          <t>3038260</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6065977</t>
+          <t>6067130</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6156638</t>
+          <t>6155573</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,59%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12885</t>
+          <t>13128</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33876</t>
+          <t>34093</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15192</t>
+          <t>15813</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35654</t>
+          <t>34882</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31506</t>
+          <t>32765</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60223</t>
+          <t>60478</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>403335</t>
+          <t>403118</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>424326</t>
+          <t>424083</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>278800</t>
+          <t>279572</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>299262</t>
+          <t>298641</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>691442</t>
+          <t>691187</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>720159</t>
+          <t>718900</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14345</t>
+          <t>13369</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35968</t>
+          <t>35875</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20223</t>
+          <t>20526</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41960</t>
+          <t>42239</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>39208</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69950</t>
+          <t>70956</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>382829</t>
+          <t>382922</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>404452</t>
+          <t>405428</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>296051</t>
+          <t>295772</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>317788</t>
+          <t>317485</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>686858</t>
+          <t>685852</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>718279</t>
+          <t>717600</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48265</t>
+          <t>47790</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81832</t>
+          <t>79873</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35988</t>
+          <t>35038</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60061</t>
+          <t>60325</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>88946</t>
+          <t>91164</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131821</t>
+          <t>132710</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>547583</t>
+          <t>549542</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>581150</t>
+          <t>581625</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>200068</t>
+          <t>199804</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>224141</t>
+          <t>225091</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>757723</t>
+          <t>756834</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>800598</t>
+          <t>798380</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,75%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64114</t>
+          <t>64688</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100903</t>
+          <t>103042</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84376</t>
+          <t>87901</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>125062</t>
+          <t>127453</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>160350</t>
+          <t>160195</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>212897</t>
+          <t>214875</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1058106</t>
+          <t>1055967</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1094895</t>
+          <t>1094321</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>641595</t>
+          <t>639204</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>682281</t>
+          <t>678756</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1712770</t>
+          <t>1710792</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1765317</t>
+          <t>1765472</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,68%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20319</t>
+          <t>21330</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41334</t>
+          <t>41131</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>129808</t>
+          <t>129866</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>175243</t>
+          <t>176243</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>158197</t>
+          <t>159678</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>212203</t>
+          <t>213102</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>469262</t>
+          <t>469465</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>490277</t>
+          <t>489266</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>586279</t>
+          <t>585279</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>631714</t>
+          <t>631656</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1059915</t>
+          <t>1059016</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1113921</t>
+          <t>1112440</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,45%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2813</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15034</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>171968</t>
+          <t>172990</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>222865</t>
+          <t>225318</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>177405</t>
+          <t>178370</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>231467</t>
+          <t>232389</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>251848</t>
+          <t>252680</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>264095</t>
+          <t>264069</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>886486</t>
+          <t>884033</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>937383</t>
+          <t>936361</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1144766</t>
+          <t>1143844</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1198828</t>
+          <t>1197863</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,04%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>196629</t>
+          <t>195556</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>259899</t>
+          <t>259231</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>507890</t>
+          <t>509160</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>598701</t>
+          <t>597297</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>724127</t>
+          <t>725819</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>835017</t>
+          <t>835219</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3162011</t>
+          <t>3162679</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3225281</t>
+          <t>3226354</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2951424</t>
+          <t>2952828</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3042235</t>
+          <t>3040965</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6137018</t>
+          <t>6136816</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6247908</t>
+          <t>6246216</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,59%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17698</t>
+          <t>16907</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38812</t>
+          <t>38060</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19019</t>
+          <t>18570</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40048</t>
+          <t>40156</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>40094</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70233</t>
+          <t>70868</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>390280</t>
+          <t>391032</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>411394</t>
+          <t>412185</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>307007</t>
+          <t>306899</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>328036</t>
+          <t>328485</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>705914</t>
+          <t>705279</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>735758</t>
+          <t>736053</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30490</t>
+          <t>31299</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14511</t>
+          <t>14589</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34502</t>
+          <t>34408</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32336</t>
+          <t>32587</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58693</t>
+          <t>59690</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>346737</t>
+          <t>345928</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>337771</t>
+          <t>337865</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>357762</t>
+          <t>357684</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>690807</t>
+          <t>689810</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>717164</t>
+          <t>716913</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,65%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20240</t>
+          <t>21891</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42312</t>
+          <t>43076</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19744</t>
+          <t>19638</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40518</t>
+          <t>41102</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46980</t>
+          <t>46873</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77996</t>
+          <t>79010</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>479602</t>
+          <t>478838</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>501674</t>
+          <t>500023</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125605</t>
+          <t>125021</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>146379</t>
+          <t>146485</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>610040</t>
+          <t>609026</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>641056</t>
+          <t>641163</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,19%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65324</t>
+          <t>64683</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98848</t>
+          <t>100053</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>88978</t>
+          <t>90612</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>129358</t>
+          <t>127849</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>163630</t>
+          <t>164513</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>216723</t>
+          <t>218567</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1050790</t>
+          <t>1049585</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1084314</t>
+          <t>1084955</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>696518</t>
+          <t>698027</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>736898</t>
+          <t>735264</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1758791</t>
+          <t>1756947</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1811884</t>
+          <t>1811001</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,67%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35735</t>
+          <t>37206</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63000</t>
+          <t>64326</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>138236</t>
+          <t>140008</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>184435</t>
+          <t>185843</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>185074</t>
+          <t>183503</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>236675</t>
+          <t>236141</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>557706</t>
+          <t>556380</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>584971</t>
+          <t>583500</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>553809</t>
+          <t>552401</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>600008</t>
+          <t>598236</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1122275</t>
+          <t>1122809</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1173876</t>
+          <t>1175447</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,5%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>11423</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>163137</t>
+          <t>161325</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>213892</t>
+          <t>215824</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>165319</t>
+          <t>165257</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>220102</t>
+          <t>220213</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>276036</t>
+          <t>275722</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>285234</t>
+          <t>285194</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>868133</t>
+          <t>866201</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>918888</t>
+          <t>920700</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1149068</t>
+          <t>1148957</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1203851</t>
+          <t>1203913</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>182057</t>
+          <t>185997</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>237958</t>
+          <t>243932</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>494142</t>
+          <t>494851</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>582954</t>
+          <t>583941</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>700256</t>
+          <t>696825</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>810815</t>
+          <t>804587</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3147764</t>
+          <t>3141790</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3203665</t>
+          <t>3199725</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2948642</t>
+          <t>2947655</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3037454</t>
+          <t>3036745</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6106503</t>
+          <t>6112731</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6217062</t>
+          <t>6220493</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,93%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>42681</t>
+          <t>44279</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32055</t>
+          <t>32705</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56868</t>
+          <t>57420</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>41992</t>
+          <t>45762</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33426</t>
+          <t>36696</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53233</t>
+          <t>57249</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>84673</t>
+          <t>90041</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69755</t>
+          <t>73956</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102987</t>
+          <t>108507</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>462531</t>
+          <t>506339</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>448344</t>
+          <t>493198</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>473157</t>
+          <t>517913</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>405475</t>
+          <t>442649</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>394234</t>
+          <t>431162</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>414041</t>
+          <t>451715</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>868006</t>
+          <t>948988</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>849692</t>
+          <t>930522</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>882924</t>
+          <t>965073</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,88%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30242</t>
+          <t>31712</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21596</t>
+          <t>23183</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41966</t>
+          <t>43323</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>49477</t>
+          <t>54807</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41025</t>
+          <t>44309</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60947</t>
+          <t>65807</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,17 +9046,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>79719</t>
+          <t>86519</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66449</t>
+          <t>72439</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96723</t>
+          <t>105791</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>421971</t>
+          <t>451500</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>410247</t>
+          <t>439889</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>430617</t>
+          <t>460029</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>333103</t>
+          <t>368336</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>321633</t>
+          <t>357336</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>341555</t>
+          <t>378834</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,17 +9159,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>755074</t>
+          <t>819836</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>738070</t>
+          <t>800564</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>768344</t>
+          <t>833916</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>45424</t>
+          <t>48726</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16878</t>
+          <t>37248</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77198</t>
+          <t>63361</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>35194</t>
+          <t>38558</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27361</t>
+          <t>29780</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44306</t>
+          <t>48465</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>80618</t>
+          <t>87284</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>73365</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119337</t>
+          <t>103245</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>622840</t>
+          <t>422886</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>591066</t>
+          <t>408251</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>651386</t>
+          <t>434364</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>131717</t>
+          <t>148939</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>122605</t>
+          <t>139032</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139550</t>
+          <t>157717</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>79,44%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>754557</t>
+          <t>571825</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>715838</t>
+          <t>555864</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>799533</t>
+          <t>585744</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>88,87%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>97060</t>
+          <t>106104</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81570</t>
+          <t>88693</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>114953</t>
+          <t>126057</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>121954</t>
+          <t>133334</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68036</t>
+          <t>116877</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>161618</t>
+          <t>150966</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>219013</t>
+          <t>239438</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>147637</t>
+          <t>214445</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>254028</t>
+          <t>268382</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>13,47%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>937759</t>
+          <t>1025739</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>919866</t>
+          <t>1005786</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>953249</t>
+          <t>1043150</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>856140</t>
+          <t>727877</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>816476</t>
+          <t>710245</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>910058</t>
+          <t>744334</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1793899</t>
+          <t>1753616</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1758884</t>
+          <t>1724672</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1865275</t>
+          <t>1778609</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>89,24%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>52433</t>
+          <t>57992</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39263</t>
+          <t>45390</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65684</t>
+          <t>73291</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>190933</t>
+          <t>202564</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>144214</t>
+          <t>185126</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>224992</t>
+          <t>224353</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>243367</t>
+          <t>260557</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>199966</t>
+          <t>235890</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>273503</t>
+          <t>285705</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>422613</t>
+          <t>509972</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>409362</t>
+          <t>494673</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>435783</t>
+          <t>522574</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>650402</t>
+          <t>628286</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>616343</t>
+          <t>606497</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>697121</t>
+          <t>645724</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1073014</t>
+          <t>1138257</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1042878</t>
+          <t>1113109</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1116415</t>
+          <t>1162924</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>83,14%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12583</t>
+          <t>13803</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>6745</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27764</t>
+          <t>26894</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>152606</t>
+          <t>166267</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>134898</t>
+          <t>148843</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>172910</t>
+          <t>187694</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>165189</t>
+          <t>180071</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>146400</t>
+          <t>159145</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>188761</t>
+          <t>203143</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>227924</t>
+          <t>223425</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>212743</t>
+          <t>210334</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>234144</t>
+          <t>230483</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>608765</t>
+          <t>678014</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>588461</t>
+          <t>656587</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>626473</t>
+          <t>695438</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>836689</t>
+          <t>901438</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>813117</t>
+          <t>878366</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>855478</t>
+          <t>922364</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,28%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>280422</t>
+          <t>302617</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>222762</t>
+          <t>268967</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>319678</t>
+          <t>334207</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>592157</t>
+          <t>641292</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>488075</t>
+          <t>602456</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>649604</t>
+          <t>679772</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>872578</t>
+          <t>943908</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>756140</t>
+          <t>889792</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>940658</t>
+          <t>993101</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3095638</t>
+          <t>3139859</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3056382</t>
+          <t>3108269</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3153298</t>
+          <t>3173509</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2985601</t>
+          <t>2994101</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2928154</t>
+          <t>2955621</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3089683</t>
+          <t>3032937</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6081240</t>
+          <t>6133961</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6013160</t>
+          <t>6084768</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6197678</t>
+          <t>6188077</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>87,43%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3577758</t>
+          <t>3635393</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6953818</t>
+          <t>7077869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
